--- a/college-posters/data/字段表_第三批.xlsx
+++ b/college-posters/data/字段表_第三批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -483,17 +483,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>QS世界大学排名</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>QS 2027 第=309名（2026年251–300区间）</t>
+          <t>汉语言文学、数学与应用数学、化学、临床医学、计算机科学与技术、历史学</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -505,17 +505,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>汉语言文学、数学与应用数学、化学、临床医学、计算机科学与技术、历史学</t>
+          <t>2024届：升学占毕业去向58.39%（其中出国（境）858人）；另一口径国内外深造49.30%（分母为毕业人数）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核报告原文（口径不一）</t>
         </is>
       </c>
     </row>
@@ -527,46 +527,46 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024届：升学占毕业去向58.39%（其中出国（境）858人）；另一口径国内外深造49.30%（分母为毕业人数）</t>
+          <t>中心校区：济南主校区；洪家楼校区：老山大文脉所在；青岛校区：依山面海的新校区</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核报告原文（口径不一）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>山东大学</t>
+          <t>西北工业大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>党政机关与国企、医疗卫生、电子信息与制造</t>
+          <t>飞行器设计与工程、飞行器动力工程、水声工程、材料科学与工程、机械设计制造及其自动化、计算机科学与技术</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>山东大学</t>
+          <t>西北工业大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中心校区：济南主校区；洪家楼校区：老山大文脉所在；青岛校区：依山面海的新校区</t>
+          <t>友谊校区：西安城内的老校区；长安校区：长安区主校区；太仓校区：长三角研究院所在地</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,73 +588,73 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>山东大学</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>农学、动物医学、食品科学与工程、农业机械化及其自动化、生物科学、农林经济管理</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>西北工业大学</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>飞行器设计与工程、飞行器动力工程、水声工程、材料科学与工程、机械设计制造及其自动化、计算机科学与技术</t>
+          <t>西校区：圆明园西路老校区；东校区：清华东路校区；涿州基地：大型农业教学实验场</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>西北工业大学</t>
+          <t>厦门大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>航空航天科研院所、国防军工企业、电子信息与互联网</t>
+          <t>化学、经济学、会计学、海洋科学、统计学、新闻学</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>西北工业大学</t>
+          <t>厦门大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>友谊校区：西安城内的老校区；长安校区：长安区主校区；太仓校区：长三角研究院所在地</t>
+          <t>芙蓉湖：思明校区中心湖；上弦场：面朝大海的运动场；嘉庚建筑：中西合璧的建筑群</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,73 +676,73 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>西北工业大学</t>
+          <t>吉林大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>化学、车辆工程、考古学、临床医学、数学与应用数学、地质学</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>吉林大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>农学、动物医学、食品科学与工程、农业机械化及其自动化、生物科学、农林经济管理</t>
+          <t>鼎新图书馆：前卫校区标志建筑；前卫校区：长春主校区；南岭校区：原吉林工业大学校区</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>中南大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>农业与生命科学院所、食品与生物企业、党政机关与国企</t>
+          <t>临床医学、冶金工程、材料科学与工程、交通运输、采矿工程、计算机科学与技术</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>中南大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>西校区：圆明园西路老校区；东校区：清华东路校区；涿州基地：大型农业教学实验场</t>
+          <t>湘雅医学院：百年医学名校；岳麓山：校园依山而建；铁道校区：原长沙铁道学院</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -764,117 +764,117 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>大连理工大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>化学工程与工艺、工程力学、船舶与海洋工程、土木工程、机械设计制造及其自动化、软件工程</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>厦门大学</t>
+          <t>大连理工大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>化学、经济学、会计学、海洋科学、统计学、新闻学</t>
+          <t>主楼：凌水校区标志建筑；西山湖：校园湖景；开发区校区：软件学院所在地</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>厦门大学</t>
+          <t>华东师范大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>金融与会计、电子信息与互联网、党政机关与国企</t>
+          <t>教育学、心理学、汉语言文学、地理科学、统计学、软件工程</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>厦门大学</t>
+          <t>华东师范大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>芙蓉湖：思明校区中心湖；上弦场：面朝大海的运动场；嘉庚建筑：中西合璧的建筑群</t>
+          <t>51.67%的本科毕业生升学深造，比2023届高近5个百分点（转载段落排版错乱）</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核报告原文（对应关系不确定）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>厦门大学</t>
+          <t>华东师范大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>丽娃河：中山北路校区名河；夏雨岛：丽娃河中的小岛；闵行校区：紫竹园区旁主校区</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>吉林大学</t>
+          <t>湖南大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>化学、车辆工程、考古学、临床医学、数学与应用数学、地质学</t>
+          <t>化学、机械设计制造及其自动化、电气工程及其自动化、车辆工程、土木工程、金融学</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -896,51 +896,51 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>吉林大学</t>
+          <t>湖南大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>汽车与先进制造、医疗卫生、党政机关与国企</t>
+          <t>岳麓书院：宋代四大书院之一；爱晚亭：“停车坐爱枫林晚”；东方红广场：湖大中心广场</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>吉林大学</t>
+          <t>华南理工大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>孙家钟、沈家骢（吉大化学，院士）；张文显（吉大法学）</t>
+          <t>建筑学、材料科学与工程、轻化工程、食品科学与工程、计算机科学与技术、电子信息工程</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核（学籍）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>吉林大学</t>
+          <t>华南理工大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -950,650 +950,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>鼎新图书馆：前卫校区标志建筑；前卫校区：长春主校区；南岭校区：原吉林工业大学校区</t>
+          <t>五山校区：林木葱郁的老校区；西湖：五山校区湖景；国际校区：番禺新校区</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>吉林大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>中南大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>QS世界大学排名</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>QS 2027 第452名</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核QS官网（仅单一来源）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>中南大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>临床医学、冶金工程、材料科学与工程、交通运输、采矿工程、计算机科学与技术</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>中南大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>医疗卫生、有色冶金与材料、轨道交通与电子信息</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>中南大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>湘雅医学院：百年医学名校；岳麓山：校园依山而建；铁道校区：原长沙铁道学院</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>中南大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>大连理工大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>QS世界大学排名</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>QS 2027 第463名</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核QS官网（仅单一来源）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>大连理工大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>化学工程与工艺、工程力学、船舶与海洋工程、土木工程、机械设计制造及其自动化、软件工程</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>大连理工大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>化工与能源、装备制造与船舶、电子信息与互联网</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>大连理工大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>知名校友</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>程耿东（大连工学院）；申长雨（大连理工本硕）</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>大连理工大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>主楼：凌水校区标志建筑；西山湖：校园湖景；开发区校区：软件学院所在地</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>大连理工大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>华东师范大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>QS、ARWU 名次未查到可靠来源，不放；双一流学科海报写3个（教育学、生态学、统计学）</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文（个数未核到）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>华东师范大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>双一流建设学科</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>教育学、生态学、统计学</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>华东师范大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>教育学、心理学、汉语言文学、地理科学、统计学、软件工程</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>华东师范大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>深造率</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>51.67%的本科毕业生升学深造，比2023届高近5个百分点（转载段落排版错乱）</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核报告原文（对应关系不确定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>华东师范大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>教育与科研、互联网与金融、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>华东师范大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>丽娃河：中山北路校区名河；夏雨岛：丽娃河中的小岛；闵行校区：紫竹园区旁主校区</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>华东师范大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>湖南大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>QS、ARWU 名次未查到可靠来源，不放；双一流学科海报写3个（化学、机械工程、电气工程）</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>湖南大学</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>双一流建设学科</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>化学、机械工程、电气工程</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>湖南大学</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>化学、机械设计制造及其自动化、电气工程及其自动化、车辆工程、土木工程、金融学</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>湖南大学</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>先进制造与汽车、电力能源、金融与会计</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>湖南大学</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>岳麓书院：宋代四大书院之一；爱晚亭：“停车坐爱枫林晚”；东方红广场：湖大中心广场</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>湖南大学</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>华南理工大学</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>建筑学、材料科学与工程、轻化工程、食品科学与工程、计算机科学与技术、电子信息工程</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>华南理工大学</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>电子信息与互联网、建筑与土木工程、大湾区先进制造</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>华南理工大学</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>五山校区：林木葱郁的老校区；西湖：五山校区湖景；国际校区：番禺新校区</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>华南理工大学</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1282,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>QS、ARWU 名次未查到可靠来源，不放；双一流学科海报写3个（化学、机械工程、电气工程）</t>
+          <t>双一流3个：化学、机械工程、电气工程</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1933,9 +1295,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -1997,9 +1359,9 @@
           <t>教育部 第二轮双一流名单（转载）</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -2157,9 +1519,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2282,12 +1644,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2915,9 +2277,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3040,12 +2402,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3382,12 +2744,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>xuanxiao.org 院校页（单一第三方来源）</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>新东方QS2027 TOP500完整版、xuanxiao.org（两源一致）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（两源一致），待核QS官网</t>
         </is>
       </c>
     </row>
@@ -3673,9 +3035,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3160,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4431,9 +3793,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4556,12 +3918,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5189,9 +4551,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5314,12 +4676,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5947,9 +5309,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6072,12 +5434,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6705,9 +6067,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6724,12 +6086,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>孙家钟、沈家骢（吉大化学，院士）；张文显（吉大法学）</t>
+          <t>张文显（1979–1982吉林大学法学硕士）；沈家骢本科为浙江大学、孙家钟学籍未核到，均已撤下</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>孙家钟 中国科学院院士；沈家骢 中国科学院院士；张文显 法学家</t>
+          <t>张文显 法学家（吉大法学硕士）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6737,9 +6099,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -6830,12 +6192,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7172,12 +6534,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>网易转载榜单（单一来源）</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>新东方QS2027 TOP500完整版、xuanxiao.org（两源一致）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（两源一致），待核QS官网</t>
         </is>
       </c>
     </row>
@@ -7463,9 +6825,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7588,12 +6950,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7930,12 +7292,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>网易转载榜单（单一来源）</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>新东方QS2027 TOP500完整版、xuanxiao.org（两源一致）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（两源一致），待核QS官网</t>
         </is>
       </c>
     </row>
@@ -8221,9 +7583,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8240,12 +7602,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>程耿东（大连工学院）；申长雨（大连理工本硕）</t>
+          <t>程耿东（北京大学本科，1964–1968在大连工学院读研究生）；申长雨学籍未核到，已撤下</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>程耿东 中国科学院院士；申长雨 中国科学院院士</t>
+          <t>程耿东 中国科学院院士（大连工学院研究生）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8253,9 +7615,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -8346,12 +7708,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8104,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>QS、ARWU 名次未查到可靠来源，不放；双一流学科海报写3个（教育学、生态学、统计学）</t>
+          <t>双一流3个：教育学、生态学、统计学</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -8755,9 +8117,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文（个数未核到）</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -8819,9 +8181,9 @@
           <t>教育部 第二轮双一流名单（转载）</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -8979,9 +8341,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -9104,12 +8466,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
